--- a/artfynd/A 37983-2023 artfynd.xlsx
+++ b/artfynd/A 37983-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37983-2023 artfynd.xlsx
+++ b/artfynd/A 37983-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112191562</v>
+        <v>112191469</v>
       </c>
       <c r="B2" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579894</v>
+        <v>579767</v>
       </c>
       <c r="R2" t="n">
-        <v>6319698</v>
+        <v>6319615</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112191509</v>
+        <v>112802292</v>
       </c>
       <c r="B3" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,36 +817,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tålebo 16:1, Sm</t>
+          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579868</v>
+        <v>579780</v>
       </c>
       <c r="R3" t="n">
-        <v>6319723</v>
+        <v>6319610</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,12 +854,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Över 10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,34 +873,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>David Ek, Matilda Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112191571</v>
+        <v>112802294</v>
       </c>
       <c r="B4" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,36 +919,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tålebo 16:1, Sm</t>
+          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579926</v>
+        <v>579777</v>
       </c>
       <c r="R4" t="n">
-        <v>6319706</v>
+        <v>6319649</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,12 +956,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 5 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,34 +975,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>David Ek, Matilda Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112191665</v>
+        <v>112191729</v>
       </c>
       <c r="B5" t="n">
-        <v>103833</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1088,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579819</v>
+        <v>579742</v>
       </c>
       <c r="R5" t="n">
-        <v>6319715</v>
+        <v>6319643</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1151,69 +1107,61 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112191647</v>
+        <v>116266062</v>
       </c>
       <c r="B6" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tålebo 16:1, Sm</t>
+          <t>sandbäckshult A, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580111</v>
+        <v>579841</v>
       </c>
       <c r="R6" t="n">
-        <v>6319851</v>
+        <v>6319444</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,12 +1185,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granskad av Johan Eklöf och Stefan Pettersson</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,34 +1204,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112191729</v>
+        <v>116266037</v>
       </c>
       <c r="B7" t="n">
-        <v>103833</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,53 +1238,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tålebo 16:1, Sm</t>
+          <t>sandbäckshult A, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579742</v>
+        <v>579841</v>
       </c>
       <c r="R7" t="n">
-        <v>6319643</v>
+        <v>6319444</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,12 +1305,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,88 +1319,84 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112191590</v>
+        <v>116266020</v>
       </c>
       <c r="B8" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tålebo 16:1, Sm</t>
+          <t>sandbäckshult A, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579912</v>
+        <v>579841</v>
       </c>
       <c r="R8" t="n">
-        <v>6319661</v>
+        <v>6319444</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,12 +1420,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,88 +1434,84 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112191611</v>
+        <v>116266071</v>
       </c>
       <c r="B9" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tålebo 16:1, Sm</t>
+          <t>sandbäckshult A, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579845</v>
+        <v>579841</v>
       </c>
       <c r="R9" t="n">
-        <v>6319618</v>
+        <v>6319444</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,12 +1535,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,88 +1549,84 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112191469</v>
+        <v>116266008</v>
       </c>
       <c r="B10" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>206002</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tålebo 16:1, Sm</t>
+          <t>sandbäckshult A, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579767</v>
+        <v>579841</v>
       </c>
       <c r="R10" t="n">
-        <v>6319615</v>
+        <v>6319444</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,12 +1650,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,34 +1664,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112802295</v>
+        <v>112191509</v>
       </c>
       <c r="B11" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,20 +1715,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
+          <t>Tålebo 16:1, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579876</v>
+        <v>579868</v>
       </c>
       <c r="R11" t="n">
-        <v>6319624</v>
+        <v>6319724</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1816,17 +1768,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,33 +1782,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Ek, Matilda Jansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112802299</v>
+        <v>112191550</v>
       </c>
       <c r="B12" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,20 +1829,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
+          <t>Tålebo 16:1, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579907</v>
+        <v>579895</v>
       </c>
       <c r="R12" t="n">
-        <v>6319638</v>
+        <v>6319698</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1923,17 +1882,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En planta</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,33 +1896,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Ek, Matilda Jansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112802297</v>
+        <v>112191571</v>
       </c>
       <c r="B13" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,20 +1943,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
+          <t>Tålebo 16:1, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579882</v>
+        <v>579926</v>
       </c>
       <c r="R13" t="n">
-        <v>6319626</v>
+        <v>6319706</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2030,17 +1996,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Över 10 plantor</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,33 +2010,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Ek, Matilda Jansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112802286</v>
+        <v>112191590</v>
       </c>
       <c r="B14" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,20 +2057,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
+          <t>Tålebo 16:1, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579850</v>
+        <v>579912</v>
       </c>
       <c r="R14" t="n">
-        <v>6319498</v>
+        <v>6319661</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2137,17 +2110,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ca 5 plantor</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,33 +2124,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Ek, Matilda Jansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112802292</v>
+        <v>112191611</v>
       </c>
       <c r="B15" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,20 +2171,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
+          <t>Tålebo 16:1, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579779</v>
+        <v>579845</v>
       </c>
       <c r="R15" t="n">
-        <v>6319611</v>
+        <v>6319618</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2244,17 +2224,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Över 10</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,33 +2238,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Ek, Matilda Jansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112802289</v>
+        <v>112191647</v>
       </c>
       <c r="B16" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,20 +2285,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
+          <t>Tålebo 16:1, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579921</v>
+        <v>580112</v>
       </c>
       <c r="R16" t="n">
-        <v>6319721</v>
+        <v>6319850</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2351,17 +2338,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ca 5 plantor</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,33 +2352,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Ek, Matilda Jansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112802285</v>
+        <v>112802284</v>
       </c>
       <c r="B17" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,17 +2402,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
+          <t>Baggemåla, Mönsterås kommun, Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579864</v>
+        <v>580112</v>
       </c>
       <c r="R17" t="n">
-        <v>6319486</v>
+        <v>6319838</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,7 +2446,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ca 5 plantor</t>
+          <t>Ca 8 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,15 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112802287</v>
+        <v>112802285</v>
       </c>
       <c r="B18" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579848</v>
+        <v>579864</v>
       </c>
       <c r="R18" t="n">
-        <v>6319508</v>
+        <v>6319487</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2575,7 +2548,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Över 10 plantor</t>
+          <t>Ca 5 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,15 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112802288</v>
+        <v>112802286</v>
       </c>
       <c r="B19" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579830</v>
+        <v>579850</v>
       </c>
       <c r="R19" t="n">
-        <v>6319630</v>
+        <v>6319498</v>
       </c>
       <c r="S19" t="n">
         <v>6</v>
@@ -2709,15 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112802291</v>
+        <v>112802287</v>
       </c>
       <c r="B20" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,13 +2712,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579846</v>
+        <v>579848</v>
       </c>
       <c r="R20" t="n">
-        <v>6319784</v>
+        <v>6319508</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2789,7 +2752,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2 plantor</t>
+          <t>Över 10 plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,15 +2779,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112802294</v>
+        <v>112802288</v>
       </c>
       <c r="B21" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,10 +2814,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579777</v>
+        <v>579830</v>
       </c>
       <c r="R21" t="n">
-        <v>6319649</v>
+        <v>6319630</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -2923,15 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112802284</v>
+        <v>112802289</v>
       </c>
       <c r="B22" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2959,17 +2912,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Baggemåla, Mönsterås kommun, Kalmar län, Sm</t>
+          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580111</v>
+        <v>579921</v>
       </c>
       <c r="R22" t="n">
-        <v>6319839</v>
+        <v>6319721</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3003,7 +2956,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ca 8 plantor</t>
+          <t>Ca 5 plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,66 +2983,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116266071</v>
+        <v>112802291</v>
       </c>
       <c r="B23" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205998</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>sandbäckshult A, Sm</t>
+          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579841</v>
+        <v>579847</v>
       </c>
       <c r="R23" t="n">
-        <v>6319444</v>
+        <v>6319784</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,12 +3048,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3129,87 +3069,64 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
+          <t>David Ek, Matilda Jansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116266008</v>
+        <v>112802295</v>
       </c>
       <c r="B24" t="n">
-        <v>56185</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206002</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>sandbäckshult A, Sm</t>
+          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579841</v>
+        <v>579876</v>
       </c>
       <c r="R24" t="n">
-        <v>6319444</v>
+        <v>6319624</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3233,12 +3150,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,87 +3171,64 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
+          <t>David Ek, Matilda Jansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116266020</v>
+        <v>112802297</v>
       </c>
       <c r="B25" t="n">
-        <v>56183</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205995</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>sandbäckshult A, Sm</t>
+          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579841</v>
+        <v>579882</v>
       </c>
       <c r="R25" t="n">
-        <v>6319444</v>
+        <v>6319626</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3353,12 +3252,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Över 10 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3369,87 +3273,64 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
+          <t>David Ek, Matilda Jansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116266037</v>
+        <v>112802299</v>
       </c>
       <c r="B26" t="n">
-        <v>56178</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100092</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>sandbäckshult A, Sm</t>
+          <t>Blomstermåla, Mönsterås kommun, Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579841</v>
+        <v>579907</v>
       </c>
       <c r="R26" t="n">
-        <v>6319444</v>
+        <v>6319638</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3473,12 +3354,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>En planta</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,87 +3375,80 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
+          <t>David Ek, Matilda Jansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116266062</v>
+        <v>112191665</v>
       </c>
       <c r="B27" t="n">
-        <v>56174</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100015</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>sandbäckshult A, Sm</t>
+          <t>Tålebo 16:1, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579841</v>
+        <v>579819</v>
       </c>
       <c r="R27" t="n">
-        <v>6319444</v>
+        <v>6319715</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3593,17 +3472,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Granskad av Johan Eklöf och Stefan Pettersson</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,23 +3486,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Alexander Eriksson, Enviro Planning</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 37983-2023 artfynd.xlsx
+++ b/artfynd/A 37983-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116266062</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116266037</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116266020</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116266071</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116266008</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191469</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191509</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1708,6 +1753,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191571</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191590</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,6 +1991,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191611</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191647</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2152,6 +2217,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802284</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2254,6 +2324,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802285</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2356,6 +2431,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802286</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,6 +2538,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802287</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2560,6 +2645,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802288</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2662,6 +2752,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802289</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2764,6 +2859,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802291</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2866,6 +2966,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802292</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2968,6 +3073,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802294</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3070,6 +3180,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802295</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3172,6 +3287,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802297</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3274,6 +3394,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112802299</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3388,6 +3513,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191665</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3502,8 +3632,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191729</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>